--- a/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-media-endoscopy.xlsx
+++ b/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-media-endoscopy.xlsx
@@ -370,7 +370,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -502,7 +502,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest|CarePlan)
+    <t xml:space="preserve">Reference(ServiceRequest|4.0.1|CarePlan|4.0.1)
 </t>
   </si>
   <si>
@@ -528,7 +528,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -599,7 +599,7 @@
     <t>高水準メディアカテゴリのコード。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/media-type</t>
+    <t>http://hl7.org/fhir/ValueSet/media-type|4.0.1</t>
   </si>
   <si>
     <t>.code</t>
@@ -647,7 +647,7 @@
     <t>画像を収集する際に使用される投影イメージングビュー。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/media-view</t>
+    <t>http://hl7.org/fhir/ValueSet/media-view|4.0.1</t>
   </si>
   <si>
     <t>DiagnosticImage.subjectOrientationCode</t>
@@ -792,7 +792,7 @@
     <t>メディアの理由。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -813,7 +813,7 @@
     <t>解剖学的位置を記述するコード。左右対称性を含む場合があります。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>targetSiteCode</t>
@@ -847,7 +847,7 @@
     <t>Media.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric|Device)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1|Device|4.0.1)
 </t>
   </si>
   <si>
